--- a/tyasa_modular/FORMADOS PERFILES TUBULARES.xlsx
+++ b/tyasa_modular/FORMADOS PERFILES TUBULARES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M860"/>
+  <dimension ref="A1:M862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42406,10 +42406,8 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" t="inlineStr">
-        <is>
-          <t>100005616</t>
-        </is>
+      <c r="A860" t="n">
+        <v>100005616</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -42454,6 +42452,106 @@
       </c>
       <c r="M860" t="n">
         <v>0.929</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>100006057</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>PT CUA 1 1/2" x 1 1/2" C20A53 DEC PINT</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Perfil Tubular Cuadrado</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>1 1/2" x 1 1/2"</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Formados</t>
+        </is>
+      </c>
+      <c r="F861" t="n">
+        <v>20</v>
+      </c>
+      <c r="G861" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H861" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I861" t="n">
+        <v>600</v>
+      </c>
+      <c r="J861" t="n">
+        <v>1</v>
+      </c>
+      <c r="K861" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L861" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M861" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>100005770</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>PT RECT 2" x 1" C20A513 DEC PINT</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Perfil Tubular Rectangular</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>2" x 1"</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Formados</t>
+        </is>
+      </c>
+      <c r="F862" t="n">
+        <v>20</v>
+      </c>
+      <c r="G862" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H862" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I862" t="n">
+        <v>600</v>
+      </c>
+      <c r="J862" t="n">
+        <v>1</v>
+      </c>
+      <c r="K862" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L862" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="M862" t="n">
+        <v>0.462</v>
       </c>
     </row>
   </sheetData>

--- a/tyasa_modular/FORMADOS PERFILES TUBULARES.xlsx
+++ b/tyasa_modular/FORMADOS PERFILES TUBULARES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M863"/>
+  <dimension ref="A1:M866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42553,10 +42553,8 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" t="inlineStr">
-        <is>
-          <t>100005640</t>
-        </is>
+      <c r="A863" t="n">
+        <v>100005640</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -42601,6 +42599,155 @@
       </c>
       <c r="M863" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>100005961</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>PT ACUA 1" x 1" C18 A513 PINT G40</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>PT ACUA 1" x 1" C18 A513 PINT G40</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>1"x1"</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Formados</t>
+        </is>
+      </c>
+      <c r="F864" t="n">
+        <v>18</v>
+      </c>
+      <c r="G864" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H864" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I864" t="n">
+        <v>600</v>
+      </c>
+      <c r="J864" t="n">
+        <v>1</v>
+      </c>
+      <c r="K864" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L864" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="M864" t="n">
+        <v>0.801</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>100005703</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Perfil Tubular Rectangular 3" x 1 1/2"</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>PT REC 3" X 1 1/2" C14 A513 SDEC</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>3" x 1 1/2"</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Formados</t>
+        </is>
+      </c>
+      <c r="F865" t="n">
+        <v>14</v>
+      </c>
+      <c r="G865" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H865" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I865" t="n">
+        <v>600</v>
+      </c>
+      <c r="J865" t="n">
+        <v>1</v>
+      </c>
+      <c r="K865" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L865" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M865" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>100007491</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>POLIN C 6" X 2" C14 A1011 DEC PINT</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>POLIN C 6" X 2" C14 A1011 DEC PINT</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>6" X 2"</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Galvanizados</t>
+        </is>
+      </c>
+      <c r="F866" t="n">
+        <v>14</v>
+      </c>
+      <c r="G866" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H866" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I866" t="n">
+        <v>600</v>
+      </c>
+      <c r="J866" t="n">
+        <v>1</v>
+      </c>
+      <c r="K866" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L866" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M866" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
